--- a/outputs/figure_source_data/source_data_fig_5_a.xlsx
+++ b/outputs/figure_source_data/source_data_fig_5_a.xlsx
@@ -571,25 +571,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="33" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="32" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="39" customWidth="1" min="5" max="5"/>
+    <col width="33" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="42" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="42" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -610,65 +611,70 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>human_seconds_per_item</t>
+          <t>human_source_workbook_average_seconds_per_authored_item</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>human_selected_seconds_per_final_item</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>mas_observed_generation_seconds</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>mas_automated_rating_seconds</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>mas_local_checks_and_audit_seconds</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>mas_total_seconds</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>mas_seconds_per_final_item</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>rating_calls</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>rating_call_seconds_assumption</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>human_minutes</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>mas_minutes</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>human_minutes_per_item</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>mas_minutes_per_item</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>time_basis</t>
         </is>
@@ -692,41 +698,44 @@
         <v>733.3</v>
       </c>
       <c r="E2" s="2" t="n">
+        <v>733.2857142857143</v>
+      </c>
+      <c r="F2" s="2" t="n">
         <v>19.06786</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="G2" s="2" t="n">
         <v>321.801816</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="H2" s="2" t="n">
         <v>8.4</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="I2" s="2" t="n">
         <v>349.269676</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="J2" s="2" t="n">
         <v>49.895668</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="L2" s="2" t="n">
         <v>40.225227</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="M2" s="2" t="n">
         <v>85.55</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="N2" s="2" t="n">
         <v>5.821161266666667</v>
       </c>
-      <c r="N2" s="2" t="n">
-        <v>12.22166666666667</v>
-      </c>
       <c r="O2" s="2" t="n">
+        <v>12.22142857142857</v>
+      </c>
+      <c r="P2" s="2" t="n">
         <v>0.8315944666666667</v>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>Human: selected-item authoring time from efficiency workbook. MAS: observed generation/explanation/test-point time + 4 QGval and 4 ULM calls per item-type bank + 60 s local checks/audit for 50 items.</t>
         </is>
@@ -750,41 +759,44 @@
         <v>1807.2</v>
       </c>
       <c r="E3" s="2" t="n">
+        <v>1807.222222222222</v>
+      </c>
+      <c r="F3" s="2" t="n">
         <v>111.798972</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="G3" s="2" t="n">
         <v>321.801816</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="H3" s="2" t="n">
         <v>21.6</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="I3" s="2" t="n">
         <v>455.2007880000001</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="J3" s="2" t="n">
         <v>25.28893266666667</v>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="L3" s="2" t="n">
         <v>40.225227</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="M3" s="2" t="n">
         <v>542.1666666666666</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="N3" s="2" t="n">
         <v>7.586679800000001</v>
       </c>
-      <c r="N3" s="2" t="n">
-        <v>30.12</v>
-      </c>
       <c r="O3" s="2" t="n">
+        <v>30.12037037037037</v>
+      </c>
+      <c r="P3" s="2" t="n">
         <v>0.4214822111111111</v>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="Q3" s="2" t="inlineStr">
         <is>
           <t>Human: selected-item authoring time from efficiency workbook. MAS: observed generation/explanation/test-point time + 4 QGval and 4 ULM calls per item-type bank + 60 s local checks/audit for 50 items.</t>
         </is>
@@ -808,41 +820,44 @@
         <v>1862.5</v>
       </c>
       <c r="E4" s="2" t="n">
+        <v>1862.5</v>
+      </c>
+      <c r="F4" s="2" t="n">
         <v>130.7923049292929</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="G4" s="2" t="n">
         <v>643.6036320000001</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="H4" s="2" t="n">
         <v>16.8</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="I4" s="2" t="n">
         <v>791.1959369292929</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="J4" s="2" t="n">
         <v>56.51399549494949</v>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="L4" s="2" t="n">
         <v>40.225227</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="M4" s="2" t="n">
         <v>434.5833333333333</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="N4" s="2" t="n">
         <v>13.18659894882155</v>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="O4" s="2" t="n">
         <v>31.04166666666667</v>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="P4" s="2" t="n">
         <v>0.9418999249158247</v>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>Human: selected-item authoring time from efficiency workbook. MAS: observed generation/explanation/test-point time + 4 QGval and 4 ULM calls per item-type bank + 60 s local checks/audit for 50 items.</t>
         </is>
@@ -866,41 +881,44 @@
         <v>786.7</v>
       </c>
       <c r="E5" s="2" t="n">
+        <v>786.6666666666666</v>
+      </c>
+      <c r="F5" s="2" t="n">
         <v>43.282635</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="G5" s="2" t="n">
         <v>321.801816</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="H5" s="2" t="n">
         <v>3.6</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="I5" s="2" t="n">
         <v>368.6844510000001</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="J5" s="2" t="n">
         <v>122.894817</v>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="L5" s="2" t="n">
         <v>40.225227</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="M5" s="2" t="n">
         <v>39.33333333333334</v>
       </c>
-      <c r="M5" s="2" t="n">
+      <c r="N5" s="2" t="n">
         <v>6.144740850000002</v>
       </c>
-      <c r="N5" s="2" t="n">
-        <v>13.11166666666667</v>
-      </c>
       <c r="O5" s="2" t="n">
+        <v>13.11111111111111</v>
+      </c>
+      <c r="P5" s="2" t="n">
         <v>2.048246950000001</v>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>Human: selected-item authoring time from efficiency workbook. MAS: observed generation/explanation/test-point time + 4 QGval and 4 ULM calls per item-type bank + 60 s local checks/audit for 50 items.</t>
         </is>
@@ -924,41 +942,44 @@
         <v>1430</v>
       </c>
       <c r="E6" s="2" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F6" s="2" t="n">
         <v>37.822632</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="G6" s="2" t="n">
         <v>321.801816</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="H6" s="2" t="n">
         <v>9.6</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="I6" s="2" t="n">
         <v>369.2244480000001</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="J6" s="2" t="n">
         <v>46.15305600000001</v>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="L6" s="2" t="n">
         <v>40.225227</v>
       </c>
-      <c r="L6" s="2" t="n">
+      <c r="M6" s="2" t="n">
         <v>190.6666666666666</v>
       </c>
-      <c r="M6" s="2" t="n">
+      <c r="N6" s="2" t="n">
         <v>6.1537408</v>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="O6" s="2" t="n">
         <v>23.83333333333333</v>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="P6" s="2" t="n">
         <v>0.7692176000000001</v>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>Human: selected-item authoring time from efficiency workbook. MAS: observed generation/explanation/test-point time + 4 QGval and 4 ULM calls per item-type bank + 60 s local checks/audit for 50 items.</t>
         </is>
